--- a/2025-MLS-projections/Japanese Catch/annual_JPN_catch.xlsx
+++ b/2025-MLS-projections/Japanese Catch/annual_JPN_catch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jon.brodziak\Desktop\2024 WCNPO MLS Rebuilding\2025 MLS projections\Japanese Catch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336554F2-249C-42B2-97A3-70F08C3348FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5410E322-25B7-4CDD-BD33-4D3EA0F9BED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8863" xr2:uid="{C9876895-7BDD-4090-9737-70E45456F99E}"/>
+    <workbookView xWindow="1097" yWindow="1097" windowWidth="12952" windowHeight="7423" xr2:uid="{C9876895-7BDD-4090-9737-70E45456F99E}"/>
   </bookViews>
   <sheets>
     <sheet name="annual_JPN_catch" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="53">
   <si>
     <t>JPNDF_qt23</t>
   </si>
@@ -163,18 +163,12 @@
     <t>Total Catch (mt)</t>
   </si>
   <si>
-    <t>Japanese Catch Biomass Sorted by Fleet Group</t>
-  </si>
-  <si>
     <t>Year</t>
   </si>
   <si>
     <t>Japanese MLS Catch Biomass by Fleet Group</t>
   </si>
   <si>
-    <t>AVERAGE</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
@@ -185,17 +179,31 @@
   </si>
   <si>
     <t>Japanese MLS Percent Catch Biomass by Fleet Group</t>
+  </si>
+  <si>
+    <t>Japanese Fleet</t>
+  </si>
+  <si>
+    <t>Source: M. Jussup, FRA Japan, 3-Feb-2025</t>
+  </si>
+  <si>
+    <t>Japanese Catch Biomass (mt) Sorted by Fleet Group</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Average</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,6 +232,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -239,7 +254,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -247,16 +262,184 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -265,7 +448,125 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -581,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568321D9-3E1B-4C09-8D31-25F2E4AAACA0}">
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="9" max="9" width="6.765625" customWidth="1"/>
@@ -592,74 +893,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="20.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="6" t="s">
-        <v>44</v>
+      <c r="A1" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="B2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="L2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-    </row>
-    <row r="3" spans="1:23" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3">
-        <v>2021</v>
-      </c>
-      <c r="C3">
-        <v>2022</v>
-      </c>
-      <c r="D3">
-        <v>2023</v>
-      </c>
-      <c r="E3">
-        <v>2024</v>
-      </c>
-      <c r="F3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3">
-        <v>2021</v>
-      </c>
-      <c r="M3">
-        <v>2022</v>
-      </c>
-      <c r="N3">
-        <v>2023</v>
-      </c>
-      <c r="O3">
-        <v>2024</v>
-      </c>
-      <c r="Q3" s="5" t="s">
+    <row r="2" spans="1:23" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A2" s="5"/>
+      <c r="I2" s="2"/>
+      <c r="Q2" s="26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="29.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="L3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="9"/>
+      <c r="Q3" s="4" t="s">
         <v>39</v>
       </c>
       <c r="R3" t="s">
@@ -681,54 +948,48 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="3">
-        <f>SUM(L4)</f>
-        <v>118.18600000000001</v>
-      </c>
-      <c r="C4" s="3">
-        <f t="shared" ref="C4:E4" si="0">SUM(M4)</f>
-        <v>74.753</v>
-      </c>
-      <c r="D4" s="3">
-        <f t="shared" si="0"/>
-        <v>128.80199999999999</v>
-      </c>
-      <c r="E4" s="3">
-        <f t="shared" si="0"/>
-        <v>82.938999999999993</v>
-      </c>
-      <c r="F4" s="3">
-        <f>SUM(B4:E4)</f>
-        <v>404.67999999999995</v>
-      </c>
-      <c r="G4" s="3">
-        <f>AVERAGE(B4:F4)</f>
-        <v>161.87199999999999</v>
-      </c>
-      <c r="I4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4">
-        <v>118.18600000000001</v>
-      </c>
-      <c r="M4">
-        <v>74.753</v>
-      </c>
-      <c r="N4">
-        <v>128.80199999999999</v>
-      </c>
-      <c r="O4">
-        <v>82.938999999999993</v>
+    <row r="4" spans="1:23" ht="29.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="21">
+        <v>2021</v>
+      </c>
+      <c r="C4" s="19">
+        <v>2022</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2023</v>
+      </c>
+      <c r="E4" s="20">
+        <v>2024</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="L4" s="19">
+        <v>2021</v>
+      </c>
+      <c r="M4" s="19">
+        <v>2022</v>
+      </c>
+      <c r="N4" s="19">
+        <v>2023</v>
+      </c>
+      <c r="O4" s="20">
+        <v>2024</v>
       </c>
       <c r="Q4" t="s">
         <v>36</v>
@@ -753,53 +1014,53 @@
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="3">
-        <f>SUM(L5:L7)</f>
-        <v>100.309</v>
-      </c>
-      <c r="C5" s="3">
-        <f t="shared" ref="C5:E5" si="1">SUM(M5:M7)</f>
-        <v>98.667000000000002</v>
-      </c>
-      <c r="D5" s="3">
-        <f t="shared" si="1"/>
-        <v>80.421000000000006</v>
-      </c>
-      <c r="E5" s="3">
-        <f t="shared" si="1"/>
-        <v>176.49799999999999</v>
-      </c>
-      <c r="F5" s="3">
-        <f t="shared" ref="F5:F11" si="2">SUM(B5:E5)</f>
-        <v>455.89499999999998</v>
-      </c>
-      <c r="G5" s="3">
-        <f t="shared" ref="G5:G11" si="3">AVERAGE(B5:E5)</f>
-        <v>113.97375</v>
-      </c>
-      <c r="I5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5">
-        <v>86.778999999999996</v>
-      </c>
-      <c r="M5">
-        <v>70.141999999999996</v>
-      </c>
-      <c r="N5">
-        <v>70.727000000000004</v>
-      </c>
-      <c r="O5">
-        <v>135.179</v>
+      <c r="A5" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="28">
+        <f>SUM(L5)</f>
+        <v>118.18600000000001</v>
+      </c>
+      <c r="C5" s="29">
+        <f>SUM(M5)</f>
+        <v>74.753</v>
+      </c>
+      <c r="D5" s="29">
+        <f>SUM(N5)</f>
+        <v>128.80199999999999</v>
+      </c>
+      <c r="E5" s="30">
+        <f>SUM(O5)</f>
+        <v>82.938999999999993</v>
+      </c>
+      <c r="F5" s="29">
+        <f>SUM(B5:E5)</f>
+        <v>404.67999999999995</v>
+      </c>
+      <c r="G5" s="31">
+        <f t="shared" ref="G5:G12" si="0">AVERAGE(B5:E5)</f>
+        <v>101.16999999999999</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="13">
+        <v>118.18600000000001</v>
+      </c>
+      <c r="M5" s="13">
+        <v>74.753</v>
+      </c>
+      <c r="N5" s="13">
+        <v>128.80199999999999</v>
+      </c>
+      <c r="O5" s="14">
+        <v>82.938999999999993</v>
       </c>
       <c r="Q5" t="s">
         <v>29</v>
@@ -824,53 +1085,53 @@
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="3">
-        <f>SUM(L8:L11)</f>
-        <v>412.13499999999999</v>
-      </c>
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:E6" si="4">SUM(M8:M11)</f>
-        <v>364.16500000000002</v>
-      </c>
-      <c r="D6" s="3">
-        <f t="shared" si="4"/>
-        <v>436.50100000000003</v>
-      </c>
-      <c r="E6" s="3">
-        <f t="shared" si="4"/>
-        <v>488.67599999999999</v>
-      </c>
-      <c r="F6" s="3">
-        <f t="shared" si="2"/>
-        <v>1701.4769999999999</v>
-      </c>
-      <c r="G6" s="3">
-        <f t="shared" si="3"/>
-        <v>425.36924999999997</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="A6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="J6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6">
-        <v>13.53</v>
-      </c>
-      <c r="M6">
-        <v>28.524999999999999</v>
-      </c>
-      <c r="N6">
-        <v>9.5950000000000006</v>
-      </c>
-      <c r="O6">
-        <v>40.944000000000003</v>
+      <c r="B6" s="32">
+        <f>SUM(L6:L8)</f>
+        <v>100.309</v>
+      </c>
+      <c r="C6" s="33">
+        <f>SUM(M6:M8)</f>
+        <v>98.667000000000002</v>
+      </c>
+      <c r="D6" s="33">
+        <f>SUM(N6:N8)</f>
+        <v>80.421000000000006</v>
+      </c>
+      <c r="E6" s="34">
+        <f>SUM(O6:O8)</f>
+        <v>176.49799999999999</v>
+      </c>
+      <c r="F6" s="33">
+        <f t="shared" ref="F6:F12" si="1">SUM(B6:E6)</f>
+        <v>455.89499999999998</v>
+      </c>
+      <c r="G6" s="35">
+        <f t="shared" si="0"/>
+        <v>113.97375</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="13">
+        <v>86.778999999999996</v>
+      </c>
+      <c r="M6" s="13">
+        <v>70.141999999999996</v>
+      </c>
+      <c r="N6" s="13">
+        <v>70.727000000000004</v>
+      </c>
+      <c r="O6" s="14">
+        <v>135.179</v>
       </c>
       <c r="Q6" t="s">
         <v>29</v>
@@ -895,53 +1156,53 @@
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="3">
-        <f>SUM(L12:L13)</f>
-        <v>71.613</v>
-      </c>
-      <c r="C7" s="3">
-        <f t="shared" ref="C7:E7" si="5">SUM(M12:M13)</f>
-        <v>36.423000000000002</v>
-      </c>
-      <c r="D7" s="3">
-        <f t="shared" si="5"/>
-        <v>27.530999999999999</v>
-      </c>
-      <c r="E7" s="3">
-        <f t="shared" si="5"/>
-        <v>26.783999999999999</v>
-      </c>
-      <c r="F7" s="3">
-        <f t="shared" si="2"/>
-        <v>162.351</v>
-      </c>
-      <c r="G7" s="3">
-        <f t="shared" si="3"/>
-        <v>40.58775</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="A7" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="32">
+        <f>SUM(L9:L12)</f>
+        <v>412.13499999999999</v>
+      </c>
+      <c r="C7" s="33">
+        <f>SUM(M9:M12)</f>
+        <v>364.16500000000002</v>
+      </c>
+      <c r="D7" s="33">
+        <f>SUM(N9:N12)</f>
+        <v>436.50100000000003</v>
+      </c>
+      <c r="E7" s="34">
+        <f>SUM(O9:O12)</f>
+        <v>488.67599999999999</v>
+      </c>
+      <c r="F7" s="33">
+        <f t="shared" si="1"/>
+        <v>1701.4769999999999</v>
+      </c>
+      <c r="G7" s="35">
+        <f t="shared" si="0"/>
+        <v>425.36924999999997</v>
+      </c>
+      <c r="I7" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="J7" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>9.9000000000000005E-2</v>
-      </c>
-      <c r="O7">
-        <v>0.375</v>
+      <c r="J7" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="13">
+        <v>13.53</v>
+      </c>
+      <c r="M7" s="13">
+        <v>28.524999999999999</v>
+      </c>
+      <c r="N7" s="13">
+        <v>9.5950000000000006</v>
+      </c>
+      <c r="O7" s="14">
+        <v>40.944000000000003</v>
       </c>
       <c r="Q7" t="s">
         <v>20</v>
@@ -966,53 +1227,53 @@
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="3">
-        <f>SUM(L14:L16)</f>
-        <v>89.24</v>
-      </c>
-      <c r="C8" s="3">
-        <f t="shared" ref="C8:E8" si="6">SUM(M14:M16)</f>
-        <v>79.738</v>
-      </c>
-      <c r="D8" s="3">
-        <f t="shared" si="6"/>
-        <v>110.13000000000001</v>
-      </c>
-      <c r="E8" s="3">
-        <f t="shared" si="6"/>
-        <v>110.13000000000001</v>
-      </c>
-      <c r="F8" s="3">
-        <f t="shared" si="2"/>
-        <v>389.238</v>
-      </c>
-      <c r="G8" s="3">
-        <f t="shared" si="3"/>
-        <v>97.3095</v>
-      </c>
-      <c r="I8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8">
-        <v>132</v>
-      </c>
-      <c r="M8">
-        <v>136</v>
-      </c>
-      <c r="N8">
-        <v>136</v>
-      </c>
-      <c r="O8">
-        <v>136</v>
+      <c r="A8" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="32">
+        <f>SUM(L13:L14)</f>
+        <v>71.613</v>
+      </c>
+      <c r="C8" s="33">
+        <f>SUM(M13:M14)</f>
+        <v>36.423000000000002</v>
+      </c>
+      <c r="D8" s="33">
+        <f>SUM(N13:N14)</f>
+        <v>27.530999999999999</v>
+      </c>
+      <c r="E8" s="34">
+        <f>SUM(O13:O14)</f>
+        <v>26.783999999999999</v>
+      </c>
+      <c r="F8" s="33">
+        <f t="shared" si="1"/>
+        <v>162.351</v>
+      </c>
+      <c r="G8" s="35">
+        <f t="shared" si="0"/>
+        <v>40.58775</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="13">
+        <v>0</v>
+      </c>
+      <c r="M8" s="13">
+        <v>0</v>
+      </c>
+      <c r="N8" s="13">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="O8" s="14">
+        <v>0.375</v>
       </c>
       <c r="Q8" t="s">
         <v>15</v>
@@ -1037,53 +1298,53 @@
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3">
-        <f>SUM(L17)</f>
-        <v>36.92</v>
-      </c>
-      <c r="C9" s="3">
-        <f t="shared" ref="C9:E9" si="7">SUM(M17)</f>
-        <v>53.64</v>
-      </c>
-      <c r="D9" s="3">
-        <f t="shared" si="7"/>
-        <v>53.64</v>
-      </c>
-      <c r="E9" s="3">
-        <f t="shared" si="7"/>
-        <v>53.64</v>
-      </c>
-      <c r="F9" s="3">
-        <f t="shared" si="2"/>
-        <v>197.83999999999997</v>
-      </c>
-      <c r="G9" s="3">
-        <f t="shared" si="3"/>
-        <v>49.459999999999994</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="A9" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="32">
+        <f>SUM(L15:L17)</f>
+        <v>89.24</v>
+      </c>
+      <c r="C9" s="33">
+        <f>SUM(M15:M17)</f>
+        <v>79.738</v>
+      </c>
+      <c r="D9" s="33">
+        <f>SUM(N15:N17)</f>
+        <v>110.13000000000001</v>
+      </c>
+      <c r="E9" s="34">
+        <f>SUM(O15:O17)</f>
+        <v>110.13000000000001</v>
+      </c>
+      <c r="F9" s="33">
+        <f t="shared" si="1"/>
+        <v>389.238</v>
+      </c>
+      <c r="G9" s="35">
+        <f t="shared" si="0"/>
+        <v>97.3095</v>
+      </c>
+      <c r="I9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J9" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9">
-        <v>111</v>
-      </c>
-      <c r="M9">
-        <v>125</v>
-      </c>
-      <c r="N9">
-        <v>125</v>
-      </c>
-      <c r="O9">
-        <v>125</v>
+      <c r="J9" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="13">
+        <v>132</v>
+      </c>
+      <c r="M9" s="13">
+        <v>136</v>
+      </c>
+      <c r="N9" s="13">
+        <v>136</v>
+      </c>
+      <c r="O9" s="14">
+        <v>136</v>
       </c>
       <c r="Q9" t="s">
         <v>8</v>
@@ -1108,53 +1369,53 @@
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="3">
+      <c r="A10" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="32">
         <f>SUM(L18)</f>
-        <v>58.08</v>
-      </c>
-      <c r="C10" s="3">
-        <f t="shared" ref="C10:E10" si="8">SUM(M18)</f>
-        <v>84.36</v>
-      </c>
-      <c r="D10" s="3">
-        <f t="shared" si="8"/>
-        <v>84.36</v>
-      </c>
-      <c r="E10" s="3">
-        <f t="shared" si="8"/>
-        <v>84.36</v>
-      </c>
-      <c r="F10" s="3">
-        <f t="shared" si="2"/>
-        <v>311.16000000000003</v>
-      </c>
-      <c r="G10" s="3">
-        <f t="shared" si="3"/>
-        <v>77.790000000000006</v>
-      </c>
-      <c r="I10" t="s">
+        <v>36.92</v>
+      </c>
+      <c r="C10" s="33">
+        <f>SUM(M18)</f>
+        <v>53.64</v>
+      </c>
+      <c r="D10" s="33">
+        <f>SUM(N18)</f>
+        <v>53.64</v>
+      </c>
+      <c r="E10" s="34">
+        <f>SUM(O18)</f>
+        <v>53.64</v>
+      </c>
+      <c r="F10" s="33">
+        <f t="shared" si="1"/>
+        <v>197.83999999999997</v>
+      </c>
+      <c r="G10" s="35">
+        <f t="shared" si="0"/>
+        <v>49.459999999999994</v>
+      </c>
+      <c r="I10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J10" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10">
-        <v>168.828</v>
-      </c>
-      <c r="M10">
-        <v>102.377</v>
-      </c>
-      <c r="N10">
-        <v>175.215</v>
-      </c>
-      <c r="O10">
-        <v>226.7</v>
+      <c r="J10" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="13">
+        <v>111</v>
+      </c>
+      <c r="M10" s="13">
+        <v>125</v>
+      </c>
+      <c r="N10" s="13">
+        <v>125</v>
+      </c>
+      <c r="O10" s="14">
+        <v>125</v>
       </c>
       <c r="Q10" t="s">
         <v>29</v>
@@ -1179,53 +1440,53 @@
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="3">
-        <f>SUM(B4:B10)</f>
-        <v>886.48299999999995</v>
-      </c>
-      <c r="C11" s="3">
-        <f t="shared" ref="C11:E11" si="9">SUM(C4:C10)</f>
-        <v>791.74600000000009</v>
-      </c>
-      <c r="D11" s="3">
-        <f t="shared" si="9"/>
-        <v>921.38499999999999</v>
-      </c>
-      <c r="E11" s="3">
-        <f t="shared" si="9"/>
-        <v>1023.027</v>
-      </c>
-      <c r="F11" s="3">
-        <f t="shared" si="2"/>
-        <v>3622.6410000000001</v>
-      </c>
-      <c r="G11" s="3">
-        <f t="shared" si="3"/>
-        <v>905.66025000000002</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="A11" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="32">
+        <f>SUM(L19)</f>
+        <v>58.08</v>
+      </c>
+      <c r="C11" s="33">
+        <f>SUM(M19)</f>
+        <v>84.36</v>
+      </c>
+      <c r="D11" s="33">
+        <f>SUM(N19)</f>
+        <v>84.36</v>
+      </c>
+      <c r="E11" s="34">
+        <f>SUM(O19)</f>
+        <v>84.36</v>
+      </c>
+      <c r="F11" s="33">
+        <f t="shared" si="1"/>
+        <v>311.16000000000003</v>
+      </c>
+      <c r="G11" s="35">
+        <f t="shared" si="0"/>
+        <v>77.790000000000006</v>
+      </c>
+      <c r="I11" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" t="s">
-        <v>18</v>
-      </c>
-      <c r="L11">
-        <v>0.307</v>
-      </c>
-      <c r="M11">
-        <v>0.78800000000000003</v>
-      </c>
-      <c r="N11">
-        <v>0.28599999999999998</v>
-      </c>
-      <c r="O11">
-        <v>0.97599999999999998</v>
+      <c r="J11" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="13">
+        <v>168.828</v>
+      </c>
+      <c r="M11" s="13">
+        <v>102.377</v>
+      </c>
+      <c r="N11" s="13">
+        <v>175.215</v>
+      </c>
+      <c r="O11" s="14">
+        <v>226.7</v>
       </c>
       <c r="Q11" t="s">
         <v>20</v>
@@ -1249,27 +1510,54 @@
         <v>0.97599999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="I12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" t="s">
-        <v>16</v>
-      </c>
-      <c r="L12">
-        <v>70.497</v>
-      </c>
-      <c r="M12">
-        <v>35.542000000000002</v>
-      </c>
-      <c r="N12">
-        <v>26.044</v>
-      </c>
-      <c r="O12">
-        <v>25.384</v>
+    <row r="12" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="36">
+        <f>SUM(B5:B11)</f>
+        <v>886.48299999999995</v>
+      </c>
+      <c r="C12" s="37">
+        <f t="shared" ref="C12:E12" si="2">SUM(C5:C11)</f>
+        <v>791.74600000000009</v>
+      </c>
+      <c r="D12" s="37">
+        <f t="shared" si="2"/>
+        <v>921.38499999999999</v>
+      </c>
+      <c r="E12" s="38">
+        <f t="shared" si="2"/>
+        <v>1023.027</v>
+      </c>
+      <c r="F12" s="37">
+        <f t="shared" si="1"/>
+        <v>3622.6410000000001</v>
+      </c>
+      <c r="G12" s="39">
+        <f t="shared" si="0"/>
+        <v>905.66025000000002</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="13">
+        <v>0.307</v>
+      </c>
+      <c r="M12" s="13">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="N12" s="13">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="O12" s="14">
+        <v>0.97599999999999998</v>
       </c>
       <c r="Q12" t="s">
         <v>15</v>
@@ -1294,26 +1582,26 @@
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="I13" t="s">
+      <c r="I13" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="J13" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" t="s">
-        <v>13</v>
-      </c>
-      <c r="L13">
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="M13">
-        <v>0.88100000000000001</v>
-      </c>
-      <c r="N13">
-        <v>1.4870000000000001</v>
-      </c>
-      <c r="O13">
-        <v>1.4</v>
+      <c r="J13" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L13" s="13">
+        <v>70.497</v>
+      </c>
+      <c r="M13" s="13">
+        <v>35.542000000000002</v>
+      </c>
+      <c r="N13" s="13">
+        <v>26.044</v>
+      </c>
+      <c r="O13" s="14">
+        <v>25.384</v>
       </c>
       <c r="Q13" t="s">
         <v>8</v>
@@ -1337,31 +1625,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A14" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I14" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14" t="s">
-        <v>11</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0.25900000000000001</v>
-      </c>
-      <c r="O14">
-        <f>N14</f>
-        <v>0.25900000000000001</v>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="I14" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="L14" s="13">
+        <v>1.1160000000000001</v>
+      </c>
+      <c r="M14" s="13">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="N14" s="13">
+        <v>1.4870000000000001</v>
+      </c>
+      <c r="O14" s="14">
+        <v>1.4</v>
       </c>
       <c r="Q14" t="s">
         <v>8</v>
@@ -1385,34 +1669,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="B15" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="I15" t="s">
+    <row r="15" spans="1:23" ht="20.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J15" t="s">
-        <v>10</v>
-      </c>
-      <c r="K15" t="s">
-        <v>9</v>
-      </c>
-      <c r="L15">
-        <v>1.1220000000000001</v>
-      </c>
-      <c r="M15">
-        <v>3.6829999999999998</v>
-      </c>
-      <c r="N15">
-        <v>4.5659999999999998</v>
-      </c>
-      <c r="O15">
-        <f t="shared" ref="O15:O16" si="10">N15</f>
-        <v>4.5659999999999998</v>
+      <c r="J15" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" s="13">
+        <v>0</v>
+      </c>
+      <c r="M15" s="13">
+        <v>0</v>
+      </c>
+      <c r="N15" s="13">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="O15" s="14">
+        <f>N15</f>
+        <v>0.25900000000000001</v>
       </c>
       <c r="Q15" t="s">
         <v>20</v>
@@ -1436,46 +1717,29 @@
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A16" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16">
-        <v>2021</v>
-      </c>
-      <c r="C16">
-        <v>2022</v>
-      </c>
-      <c r="D16">
-        <v>2023</v>
-      </c>
-      <c r="E16">
-        <v>2024</v>
-      </c>
-      <c r="F16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" t="s">
+    <row r="16" spans="1:23" ht="21" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A16" s="2"/>
+      <c r="I16" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J16" t="s">
-        <v>7</v>
-      </c>
-      <c r="K16" t="s">
-        <v>6</v>
-      </c>
-      <c r="L16">
-        <v>88.117999999999995</v>
-      </c>
-      <c r="M16">
-        <v>76.055000000000007</v>
-      </c>
-      <c r="N16">
-        <v>105.30500000000001</v>
-      </c>
-      <c r="O16">
-        <f t="shared" si="10"/>
-        <v>105.30500000000001</v>
+      <c r="J16" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="L16" s="13">
+        <v>1.1220000000000001</v>
+      </c>
+      <c r="M16" s="13">
+        <v>3.6829999999999998</v>
+      </c>
+      <c r="N16" s="13">
+        <v>4.5659999999999998</v>
+      </c>
+      <c r="O16" s="14">
+        <f t="shared" ref="O16:O17" si="3">N16</f>
+        <v>4.5659999999999998</v>
       </c>
       <c r="Q16" t="s">
         <v>5</v>
@@ -1499,50 +1763,36 @@
         <v>53.64</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="8">
-        <f>B4/B$11</f>
-        <v>0.1333200975089201</v>
-      </c>
-      <c r="C17" s="8">
-        <f>C4/C$11</f>
-        <v>9.4415380690271875E-2</v>
-      </c>
-      <c r="D17" s="8">
-        <f t="shared" ref="D17:F17" si="11">D4/D$11</f>
-        <v>0.13979172658552069</v>
-      </c>
-      <c r="E17" s="8">
-        <f t="shared" si="11"/>
-        <v>8.1072151565892189E-2</v>
-      </c>
-      <c r="F17" s="8">
-        <f t="shared" si="11"/>
-        <v>0.11170855737568253</v>
-      </c>
-      <c r="I17" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17" t="s">
-        <v>4</v>
-      </c>
-      <c r="K17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17">
-        <v>36.92</v>
-      </c>
-      <c r="M17">
-        <v>53.64</v>
-      </c>
-      <c r="N17">
-        <v>53.64</v>
-      </c>
-      <c r="O17">
-        <v>53.64</v>
+    <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="6"/>
+      <c r="I17" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="L17" s="13">
+        <v>88.117999999999995</v>
+      </c>
+      <c r="M17" s="13">
+        <v>76.055000000000007</v>
+      </c>
+      <c r="N17" s="13">
+        <v>105.30500000000001</v>
+      </c>
+      <c r="O17" s="14">
+        <f t="shared" si="3"/>
+        <v>105.30500000000001</v>
       </c>
       <c r="Q17" t="s">
         <v>2</v>
@@ -1566,50 +1816,45 @@
         <v>84.36</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="8">
-        <f t="shared" ref="B18:F24" si="12">B5/B$11</f>
-        <v>0.11315389014792163</v>
-      </c>
-      <c r="C18" s="8">
-        <f t="shared" si="12"/>
-        <v>0.12461951181313198</v>
-      </c>
-      <c r="D18" s="8">
-        <f t="shared" si="12"/>
-        <v>8.7282731974147626E-2</v>
-      </c>
-      <c r="E18" s="8">
-        <f t="shared" si="12"/>
-        <v>0.17252526081911815</v>
-      </c>
-      <c r="F18" s="8">
-        <f t="shared" si="12"/>
-        <v>0.12584603332209843</v>
-      </c>
-      <c r="I18" t="s">
-        <v>2</v>
-      </c>
-      <c r="J18" t="s">
-        <v>1</v>
-      </c>
-      <c r="K18" t="s">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>58.08</v>
-      </c>
-      <c r="M18">
-        <v>84.36</v>
-      </c>
-      <c r="N18">
-        <v>84.36</v>
-      </c>
-      <c r="O18">
-        <v>84.36</v>
+    <row r="18" spans="1:23" ht="29.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="11">
+        <v>2021</v>
+      </c>
+      <c r="C18" s="11">
+        <v>2022</v>
+      </c>
+      <c r="D18" s="11">
+        <v>2023</v>
+      </c>
+      <c r="E18" s="11">
+        <v>2024</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="13">
+        <v>36.92</v>
+      </c>
+      <c r="M18" s="13">
+        <v>53.64</v>
+      </c>
+      <c r="N18" s="13">
+        <v>53.64</v>
+      </c>
+      <c r="O18" s="14">
+        <v>53.64</v>
       </c>
       <c r="Q18" t="s">
         <v>20</v>
@@ -1633,55 +1878,77 @@
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="8">
-        <f t="shared" si="12"/>
-        <v>0.46491021260418985</v>
-      </c>
-      <c r="C19" s="8">
-        <f t="shared" si="12"/>
-        <v>0.45995180272461117</v>
-      </c>
-      <c r="D19" s="8">
-        <f t="shared" si="12"/>
-        <v>0.47374441737167422</v>
-      </c>
-      <c r="E19" s="8">
-        <f t="shared" si="12"/>
-        <v>0.47767654226134793</v>
-      </c>
-      <c r="F19" s="8">
-        <f t="shared" si="12"/>
-        <v>0.46967861292355489</v>
+    <row r="19" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="41">
+        <f>B5/B$12</f>
+        <v>0.1333200975089201</v>
+      </c>
+      <c r="C19" s="41">
+        <f>C5/C$12</f>
+        <v>9.4415380690271875E-2</v>
+      </c>
+      <c r="D19" s="41">
+        <f>D5/D$12</f>
+        <v>0.13979172658552069</v>
+      </c>
+      <c r="E19" s="41">
+        <f>E5/E$12</f>
+        <v>8.1072151565892189E-2</v>
+      </c>
+      <c r="F19" s="42">
+        <f>AVERAGE(B19:E19)</f>
+        <v>0.11214983908765122</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="J19" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="L19" s="16">
+        <v>58.08</v>
+      </c>
+      <c r="M19" s="16">
+        <v>84.36</v>
+      </c>
+      <c r="N19" s="16">
+        <v>84.36</v>
+      </c>
+      <c r="O19" s="17">
+        <v>84.36</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="8">
-        <f t="shared" si="12"/>
-        <v>8.0783275031782897E-2</v>
-      </c>
-      <c r="C20" s="8">
-        <f t="shared" si="12"/>
-        <v>4.6003389976078182E-2</v>
-      </c>
-      <c r="D20" s="8">
-        <f t="shared" si="12"/>
-        <v>2.9880017582226755E-2</v>
-      </c>
-      <c r="E20" s="8">
-        <f t="shared" si="12"/>
-        <v>2.6181127184326511E-2</v>
-      </c>
-      <c r="F20" s="8">
-        <f t="shared" si="12"/>
-        <v>4.4815646927200345E-2</v>
-      </c>
+      <c r="A20" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="43">
+        <f>B6/B$12</f>
+        <v>0.11315389014792163</v>
+      </c>
+      <c r="C20" s="43">
+        <f>C6/C$12</f>
+        <v>0.12461951181313198</v>
+      </c>
+      <c r="D20" s="43">
+        <f>D6/D$12</f>
+        <v>8.7282731974147626E-2</v>
+      </c>
+      <c r="E20" s="43">
+        <f>E6/E$12</f>
+        <v>0.17252526081911815</v>
+      </c>
+      <c r="F20" s="44">
+        <f t="shared" ref="F20:F25" si="4">AVERAGE(B20:E20)</f>
+        <v>0.12439534868857985</v>
+      </c>
+      <c r="G20" s="40"/>
       <c r="T20">
         <v>2021</v>
       </c>
@@ -1696,121 +1963,171 @@
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="8">
-        <f t="shared" si="12"/>
-        <v>0.10066746908852173</v>
-      </c>
-      <c r="C21" s="8">
-        <f t="shared" si="12"/>
-        <v>0.10071159184890102</v>
-      </c>
-      <c r="D21" s="8">
-        <f t="shared" si="12"/>
-        <v>0.11952658226474276</v>
-      </c>
-      <c r="E21" s="8">
-        <f t="shared" si="12"/>
-        <v>0.10765111771243575</v>
-      </c>
-      <c r="F21" s="8">
-        <f t="shared" si="12"/>
-        <v>0.10744592135958268</v>
+      <c r="A21" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="43">
+        <f>B7/B$12</f>
+        <v>0.46491021260418985</v>
+      </c>
+      <c r="C21" s="43">
+        <f>C7/C$12</f>
+        <v>0.45995180272461117</v>
+      </c>
+      <c r="D21" s="43">
+        <f>D7/D$12</f>
+        <v>0.47374441737167422</v>
+      </c>
+      <c r="E21" s="43">
+        <f>E7/E$12</f>
+        <v>0.47767654226134793</v>
+      </c>
+      <c r="F21" s="44">
+        <f t="shared" si="4"/>
+        <v>0.46907074374045576</v>
       </c>
       <c r="S21" t="s">
         <v>41</v>
       </c>
-      <c r="T21" s="4">
+      <c r="T21" s="3">
         <f>SUM(T4:T18)</f>
         <v>886.48299999999995</v>
       </c>
-      <c r="U21" s="4">
-        <f t="shared" ref="U21:W21" si="13">SUM(U4:U18)</f>
+      <c r="U21" s="3">
+        <f t="shared" ref="U21:W21" si="5">SUM(U4:U18)</f>
         <v>791.74599999999987</v>
       </c>
-      <c r="V21" s="4">
-        <f t="shared" si="13"/>
+      <c r="V21" s="3">
+        <f t="shared" si="5"/>
         <v>921.38499999999999</v>
       </c>
-      <c r="W21" s="4">
-        <f t="shared" si="13"/>
+      <c r="W21" s="3">
+        <f t="shared" si="5"/>
         <v>912.89700000000005</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
+      <c r="A22" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="43">
+        <f>B8/B$12</f>
+        <v>8.0783275031782897E-2</v>
+      </c>
+      <c r="C22" s="43">
+        <f>C8/C$12</f>
+        <v>4.6003389976078182E-2</v>
+      </c>
+      <c r="D22" s="43">
+        <f>D8/D$12</f>
+        <v>2.9880017582226755E-2</v>
+      </c>
+      <c r="E22" s="43">
+        <f>E8/E$12</f>
+        <v>2.6181127184326511E-2</v>
+      </c>
+      <c r="F22" s="44">
+        <f t="shared" si="4"/>
+        <v>4.5711952443603585E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A23" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="43">
+        <f>B9/B$12</f>
+        <v>0.10066746908852173</v>
+      </c>
+      <c r="C23" s="43">
+        <f>C9/C$12</f>
+        <v>0.10071159184890102</v>
+      </c>
+      <c r="D23" s="43">
+        <f>D9/D$12</f>
+        <v>0.11952658226474276</v>
+      </c>
+      <c r="E23" s="43">
+        <f>E9/E$12</f>
+        <v>0.10765111771243575</v>
+      </c>
+      <c r="F23" s="44">
+        <f t="shared" si="4"/>
+        <v>0.10713919022865032</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A24" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="8">
-        <f t="shared" si="12"/>
+      <c r="B24" s="43">
+        <f>B10/B$12</f>
         <v>4.1647724773063902E-2</v>
       </c>
-      <c r="C22" s="8">
-        <f t="shared" si="12"/>
+      <c r="C24" s="43">
+        <f>C10/C$12</f>
         <v>6.7749000310705701E-2</v>
       </c>
-      <c r="D22" s="8">
-        <f t="shared" si="12"/>
+      <c r="D24" s="43">
+        <f>D10/D$12</f>
         <v>5.8216706371386553E-2</v>
       </c>
-      <c r="E22" s="8">
-        <f t="shared" si="12"/>
+      <c r="E24" s="43">
+        <f>E10/E$12</f>
         <v>5.2432633742804442E-2</v>
       </c>
-      <c r="F22" s="8">
-        <f t="shared" si="12"/>
-        <v>5.4612091013158622E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
+      <c r="F24" s="44">
+        <f t="shared" si="4"/>
+        <v>5.5011516299490151E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="8">
-        <f t="shared" si="12"/>
+      <c r="B25" s="45">
+        <f>B11/B$12</f>
         <v>6.5517330845599978E-2</v>
       </c>
-      <c r="C23" s="8">
-        <f t="shared" si="12"/>
+      <c r="C25" s="45">
+        <f>C11/C$12</f>
         <v>0.10654932263630001</v>
       </c>
-      <c r="D23" s="8">
-        <f t="shared" si="12"/>
+      <c r="D25" s="45">
+        <f>D11/D$12</f>
         <v>9.1557817850301454E-2</v>
       </c>
-      <c r="E23" s="8">
-        <f t="shared" si="12"/>
+      <c r="E25" s="45">
+        <f>E11/E$12</f>
         <v>8.2461166714074996E-2</v>
       </c>
-      <c r="F23" s="8">
-        <f t="shared" si="12"/>
-        <v>8.5893137078722412E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="8">
-        <f t="shared" si="12"/>
+      <c r="F25" s="46">
+        <f t="shared" si="4"/>
+        <v>8.6521409511569114E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="45">
+        <f>B12/B$12</f>
         <v>1</v>
       </c>
-      <c r="C24" s="8">
-        <f t="shared" si="12"/>
+      <c r="C26" s="45">
+        <f>C12/C$12</f>
         <v>1</v>
       </c>
-      <c r="D24" s="8">
-        <f t="shared" si="12"/>
+      <c r="D26" s="45">
+        <f>D12/D$12</f>
         <v>1</v>
       </c>
-      <c r="E24" s="8">
-        <f t="shared" si="12"/>
+      <c r="E26" s="45">
+        <f>E12/E$12</f>
         <v>1</v>
       </c>
-      <c r="F24" s="8">
-        <f t="shared" si="12"/>
+      <c r="F26" s="47">
+        <f>F12/F$12</f>
         <v>1</v>
       </c>
     </row>
@@ -1819,9 +2136,9 @@
     <sortCondition ref="R4:R12"/>
   </sortState>
   <mergeCells count="3">
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="B17:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2068,7 +2385,7 @@
         <v>25.384</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
@@ -2094,7 +2411,7 @@
         <v>1.4</v>
       </c>
       <c r="I11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">

--- a/2025-MLS-projections/Japanese Catch/annual_JPN_catch.xlsx
+++ b/2025-MLS-projections/Japanese Catch/annual_JPN_catch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jon.brodziak\Desktop\2024 WCNPO MLS Rebuilding\2025 MLS projections\Japanese Catch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5410E322-25B7-4CDD-BD33-4D3EA0F9BED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A55672-1FEB-4DF1-84C8-840A754DDB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1097" yWindow="1097" windowWidth="12952" windowHeight="7423" xr2:uid="{C9876895-7BDD-4090-9737-70E45456F99E}"/>
+    <workbookView xWindow="1234" yWindow="429" windowWidth="13663" windowHeight="8185" xr2:uid="{C9876895-7BDD-4090-9737-70E45456F99E}"/>
   </bookViews>
   <sheets>
     <sheet name="annual_JPN_catch" sheetId="1" r:id="rId1"/>
@@ -436,7 +436,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -449,20 +449,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -473,12 +464,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -565,6 +550,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -882,10 +876,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568321D9-3E1B-4C09-8D31-25F2E4AAACA0}">
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:W34"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="9" max="9" width="6.765625" customWidth="1"/>
+    <col min="9" max="9" width="9.921875" customWidth="1"/>
     <col min="11" max="11" width="16.4609375" customWidth="1"/>
     <col min="12" max="15" width="7.84375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.84375" customWidth="1"/>
@@ -906,26 +900,26 @@
     <row r="2" spans="1:23" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="5"/>
       <c r="I2" s="2"/>
-      <c r="Q2" s="26" t="s">
+      <c r="Q2" s="21" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="29.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="6"/>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="45"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="9"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="45"/>
       <c r="Q3" s="4" t="s">
         <v>39</v>
       </c>
@@ -949,46 +943,46 @@
       </c>
     </row>
     <row r="4" spans="1:23" ht="29.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="16">
         <v>2021</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="14">
         <v>2022</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="14">
         <v>2023</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="15">
         <v>2024</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="K4" s="22" t="s">
+      <c r="K4" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="L4" s="19">
+      <c r="L4" s="14">
         <v>2021</v>
       </c>
-      <c r="M4" s="19">
+      <c r="M4" s="14">
         <v>2022</v>
       </c>
-      <c r="N4" s="19">
+      <c r="N4" s="14">
         <v>2023</v>
       </c>
-      <c r="O4" s="20">
+      <c r="O4" s="15">
         <v>2024</v>
       </c>
       <c r="Q4" t="s">
@@ -1014,52 +1008,52 @@
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="23">
         <f>SUM(L5)</f>
         <v>118.18600000000001</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="24">
         <f>SUM(M5)</f>
         <v>74.753</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="24">
         <f>SUM(N5)</f>
         <v>128.80199999999999</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="25">
         <f>SUM(O5)</f>
         <v>82.938999999999993</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="24">
         <f>SUM(B5:E5)</f>
         <v>404.67999999999995</v>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="26">
         <f t="shared" ref="G5:G12" si="0">AVERAGE(B5:E5)</f>
         <v>101.16999999999999</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="J5" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="23" t="s">
+      <c r="K5" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="28">
         <v>118.18600000000001</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="28">
         <v>74.753</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="28">
         <v>128.80199999999999</v>
       </c>
-      <c r="O5" s="14">
+      <c r="O5" s="29">
         <v>82.938999999999993</v>
       </c>
       <c r="Q5" t="s">
@@ -1085,52 +1079,52 @@
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="27">
         <f>SUM(L6:L8)</f>
         <v>100.309</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="28">
         <f>SUM(M6:M8)</f>
         <v>98.667000000000002</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="28">
         <f>SUM(N6:N8)</f>
         <v>80.421000000000006</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="29">
         <f>SUM(O6:O8)</f>
         <v>176.49799999999999</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="28">
         <f t="shared" ref="F6:F12" si="1">SUM(B6:E6)</f>
         <v>455.89499999999998</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="30">
         <f t="shared" si="0"/>
         <v>113.97375</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="24" t="s">
+      <c r="J6" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="K6" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="28">
         <v>86.778999999999996</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="28">
         <v>70.141999999999996</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="28">
         <v>70.727000000000004</v>
       </c>
-      <c r="O6" s="14">
+      <c r="O6" s="29">
         <v>135.179</v>
       </c>
       <c r="Q6" t="s">
@@ -1156,52 +1150,52 @@
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="27">
         <f>SUM(L9:L12)</f>
         <v>412.13499999999999</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="28">
         <f>SUM(M9:M12)</f>
         <v>364.16500000000002</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="28">
         <f>SUM(N9:N12)</f>
         <v>436.50100000000003</v>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="29">
         <f>SUM(O9:O12)</f>
         <v>488.67599999999999</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="28">
         <f t="shared" si="1"/>
         <v>1701.4769999999999</v>
       </c>
-      <c r="G7" s="35">
+      <c r="G7" s="30">
         <f t="shared" si="0"/>
         <v>425.36924999999997</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="J7" s="24" t="s">
+      <c r="J7" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="K7" s="24" t="s">
+      <c r="K7" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="28">
         <v>13.53</v>
       </c>
-      <c r="M7" s="13">
+      <c r="M7" s="28">
         <v>28.524999999999999</v>
       </c>
-      <c r="N7" s="13">
+      <c r="N7" s="28">
         <v>9.5950000000000006</v>
       </c>
-      <c r="O7" s="14">
+      <c r="O7" s="29">
         <v>40.944000000000003</v>
       </c>
       <c r="Q7" t="s">
@@ -1227,52 +1221,52 @@
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="27">
         <f>SUM(L13:L14)</f>
         <v>71.613</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="28">
         <f>SUM(M13:M14)</f>
         <v>36.423000000000002</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="28">
         <f>SUM(N13:N14)</f>
         <v>27.530999999999999</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="29">
         <f>SUM(O13:O14)</f>
         <v>26.783999999999999</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="28">
         <f t="shared" si="1"/>
         <v>162.351</v>
       </c>
-      <c r="G8" s="35">
+      <c r="G8" s="30">
         <f t="shared" si="0"/>
         <v>40.58775</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="24" t="s">
+      <c r="J8" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="K8" s="24" t="s">
+      <c r="K8" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="10">
         <v>0</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="10">
         <v>0</v>
       </c>
-      <c r="N8" s="13">
+      <c r="N8" s="28">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="O8" s="14">
+      <c r="O8" s="29">
         <v>0.375</v>
       </c>
       <c r="Q8" t="s">
@@ -1298,52 +1292,52 @@
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="27">
         <f>SUM(L15:L17)</f>
         <v>89.24</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="28">
         <f>SUM(M15:M17)</f>
         <v>79.738</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="28">
         <f>SUM(N15:N17)</f>
         <v>110.13000000000001</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="29">
         <f>SUM(O15:O17)</f>
         <v>110.13000000000001</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="28">
         <f t="shared" si="1"/>
         <v>389.238</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="30">
         <f t="shared" si="0"/>
         <v>97.3095</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="J9" s="24" t="s">
+      <c r="J9" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="24" t="s">
+      <c r="K9" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="10">
         <v>132</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="10">
         <v>136</v>
       </c>
-      <c r="N9" s="13">
+      <c r="N9" s="10">
         <v>136</v>
       </c>
-      <c r="O9" s="14">
+      <c r="O9" s="11">
         <v>136</v>
       </c>
       <c r="Q9" t="s">
@@ -1369,52 +1363,52 @@
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="32">
-        <f>SUM(L18)</f>
+      <c r="B10" s="27">
+        <f t="shared" ref="B10:E11" si="2">SUM(L18)</f>
         <v>36.92</v>
       </c>
-      <c r="C10" s="33">
-        <f>SUM(M18)</f>
+      <c r="C10" s="28">
+        <f t="shared" si="2"/>
         <v>53.64</v>
       </c>
-      <c r="D10" s="33">
-        <f>SUM(N18)</f>
+      <c r="D10" s="28">
+        <f t="shared" si="2"/>
         <v>53.64</v>
       </c>
-      <c r="E10" s="34">
-        <f>SUM(O18)</f>
+      <c r="E10" s="29">
+        <f t="shared" si="2"/>
         <v>53.64</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="28">
         <f t="shared" si="1"/>
         <v>197.83999999999997</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="30">
         <f t="shared" si="0"/>
         <v>49.459999999999994</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="24" t="s">
+      <c r="J10" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="24" t="s">
+      <c r="K10" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="10">
         <v>111</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="10">
         <v>125</v>
       </c>
-      <c r="N10" s="13">
+      <c r="N10" s="10">
         <v>125</v>
       </c>
-      <c r="O10" s="14">
+      <c r="O10" s="11">
         <v>125</v>
       </c>
       <c r="Q10" t="s">
@@ -1440,52 +1434,52 @@
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="32">
-        <f>SUM(L19)</f>
+      <c r="B11" s="27">
+        <f t="shared" si="2"/>
         <v>58.08</v>
       </c>
-      <c r="C11" s="33">
-        <f>SUM(M19)</f>
+      <c r="C11" s="28">
+        <f t="shared" si="2"/>
         <v>84.36</v>
       </c>
-      <c r="D11" s="33">
-        <f>SUM(N19)</f>
+      <c r="D11" s="28">
+        <f t="shared" si="2"/>
         <v>84.36</v>
       </c>
-      <c r="E11" s="34">
-        <f>SUM(O19)</f>
+      <c r="E11" s="29">
+        <f t="shared" si="2"/>
         <v>84.36</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="28">
         <f t="shared" si="1"/>
         <v>311.16000000000003</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="30">
         <f t="shared" si="0"/>
         <v>77.790000000000006</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="24" t="s">
+      <c r="K11" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="28">
         <v>168.828</v>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="28">
         <v>102.377</v>
       </c>
-      <c r="N11" s="13">
+      <c r="N11" s="28">
         <v>175.215</v>
       </c>
-      <c r="O11" s="14">
+      <c r="O11" s="29">
         <v>226.7</v>
       </c>
       <c r="Q11" t="s">
@@ -1511,52 +1505,52 @@
       </c>
     </row>
     <row r="12" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="36">
+      <c r="B12" s="31">
         <f>SUM(B5:B11)</f>
         <v>886.48299999999995</v>
       </c>
-      <c r="C12" s="37">
-        <f t="shared" ref="C12:E12" si="2">SUM(C5:C11)</f>
+      <c r="C12" s="32">
+        <f t="shared" ref="C12:E12" si="3">SUM(C5:C11)</f>
         <v>791.74600000000009</v>
       </c>
-      <c r="D12" s="37">
-        <f t="shared" si="2"/>
+      <c r="D12" s="32">
+        <f t="shared" si="3"/>
         <v>921.38499999999999</v>
       </c>
-      <c r="E12" s="38">
-        <f t="shared" si="2"/>
+      <c r="E12" s="33">
+        <f t="shared" si="3"/>
         <v>1023.027</v>
       </c>
-      <c r="F12" s="37">
+      <c r="F12" s="32">
         <f t="shared" si="1"/>
         <v>3622.6410000000001</v>
       </c>
-      <c r="G12" s="39">
+      <c r="G12" s="34">
         <f t="shared" si="0"/>
         <v>905.66025000000002</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="J12" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K12" s="24" t="s">
+      <c r="K12" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="L12" s="13">
+      <c r="L12" s="28">
         <v>0.307</v>
       </c>
-      <c r="M12" s="13">
+      <c r="M12" s="28">
         <v>0.78800000000000003</v>
       </c>
-      <c r="N12" s="13">
+      <c r="N12" s="28">
         <v>0.28599999999999998</v>
       </c>
-      <c r="O12" s="14">
+      <c r="O12" s="29">
         <v>0.97599999999999998</v>
       </c>
       <c r="Q12" t="s">
@@ -1582,25 +1576,25 @@
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="J13" s="24" t="s">
+      <c r="J13" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="24" t="s">
+      <c r="K13" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="28">
         <v>70.497</v>
       </c>
-      <c r="M13" s="13">
+      <c r="M13" s="28">
         <v>35.542000000000002</v>
       </c>
-      <c r="N13" s="13">
+      <c r="N13" s="28">
         <v>26.044</v>
       </c>
-      <c r="O13" s="14">
+      <c r="O13" s="29">
         <v>25.384</v>
       </c>
       <c r="Q13" t="s">
@@ -1626,25 +1620,25 @@
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="24" t="s">
+      <c r="J14" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="K14" s="24" t="s">
+      <c r="K14" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="28">
         <v>1.1160000000000001</v>
       </c>
-      <c r="M14" s="13">
+      <c r="M14" s="28">
         <v>0.88100000000000001</v>
       </c>
-      <c r="N14" s="13">
+      <c r="N14" s="28">
         <v>1.4870000000000001</v>
       </c>
-      <c r="O14" s="14">
+      <c r="O14" s="29">
         <v>1.4</v>
       </c>
       <c r="Q14" t="s">
@@ -1673,25 +1667,25 @@
       <c r="A15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="I15" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J15" s="24" t="s">
+      <c r="J15" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K15" s="24" t="s">
+      <c r="K15" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="10">
         <v>0</v>
       </c>
-      <c r="M15" s="13">
+      <c r="M15" s="10">
         <v>0</v>
       </c>
-      <c r="N15" s="13">
+      <c r="N15" s="28">
         <v>0.25900000000000001</v>
       </c>
-      <c r="O15" s="14">
+      <c r="O15" s="29">
         <f>N15</f>
         <v>0.25900000000000001</v>
       </c>
@@ -1719,26 +1713,26 @@
     </row>
     <row r="16" spans="1:23" ht="21" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A16" s="2"/>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J16" s="24" t="s">
+      <c r="J16" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="K16" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="L16" s="13">
+      <c r="L16" s="28">
         <v>1.1220000000000001</v>
       </c>
-      <c r="M16" s="13">
+      <c r="M16" s="28">
         <v>3.6829999999999998</v>
       </c>
-      <c r="N16" s="13">
+      <c r="N16" s="28">
         <v>4.5659999999999998</v>
       </c>
-      <c r="O16" s="14">
-        <f t="shared" ref="O16:O17" si="3">N16</f>
+      <c r="O16" s="29">
+        <f t="shared" ref="O16:O17" si="4">N16</f>
         <v>4.5659999999999998</v>
       </c>
       <c r="Q16" t="s">
@@ -1765,33 +1759,33 @@
     </row>
     <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="6"/>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="9"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="45"/>
       <c r="F17" s="6"/>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J17" s="24" t="s">
+      <c r="J17" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="K17" s="24" t="s">
+      <c r="K17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="L17" s="13">
+      <c r="L17" s="28">
         <v>88.117999999999995</v>
       </c>
-      <c r="M17" s="13">
+      <c r="M17" s="28">
         <v>76.055000000000007</v>
       </c>
-      <c r="N17" s="13">
+      <c r="N17" s="28">
         <v>105.30500000000001</v>
       </c>
-      <c r="O17" s="14">
-        <f t="shared" si="3"/>
+      <c r="O17" s="29">
+        <f t="shared" si="4"/>
         <v>105.30500000000001</v>
       </c>
       <c r="Q17" t="s">
@@ -1817,43 +1811,43 @@
       </c>
     </row>
     <row r="18" spans="1:23" ht="29.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="8">
         <v>2021</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="8">
         <v>2022</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="8">
         <v>2023</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="8">
         <v>2024</v>
       </c>
-      <c r="F18" s="23" t="s">
+      <c r="F18" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="J18" s="24" t="s">
+      <c r="J18" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="K18" s="24" t="s">
+      <c r="K18" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="13">
+      <c r="L18" s="28">
         <v>36.92</v>
       </c>
-      <c r="M18" s="13">
+      <c r="M18" s="28">
         <v>53.64</v>
       </c>
-      <c r="N18" s="13">
+      <c r="N18" s="28">
         <v>53.64</v>
       </c>
-      <c r="O18" s="14">
+      <c r="O18" s="29">
         <v>53.64</v>
       </c>
       <c r="Q18" t="s">
@@ -1879,76 +1873,76 @@
       </c>
     </row>
     <row r="19" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="41">
-        <f>B5/B$12</f>
+      <c r="B19" s="36">
+        <f t="shared" ref="B19:E26" si="5">B5/B$12</f>
         <v>0.1333200975089201</v>
       </c>
-      <c r="C19" s="41">
-        <f>C5/C$12</f>
+      <c r="C19" s="36">
+        <f t="shared" si="5"/>
         <v>9.4415380690271875E-2</v>
       </c>
-      <c r="D19" s="41">
-        <f>D5/D$12</f>
+      <c r="D19" s="36">
+        <f t="shared" si="5"/>
         <v>0.13979172658552069</v>
       </c>
-      <c r="E19" s="41">
-        <f>E5/E$12</f>
+      <c r="E19" s="36">
+        <f t="shared" si="5"/>
         <v>8.1072151565892189E-2</v>
       </c>
-      <c r="F19" s="42">
+      <c r="F19" s="37">
         <f>AVERAGE(B19:E19)</f>
         <v>0.11214983908765122</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="I19" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="K19" s="25" t="s">
+      <c r="K19" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="32">
         <v>58.08</v>
       </c>
-      <c r="M19" s="16">
+      <c r="M19" s="32">
         <v>84.36</v>
       </c>
-      <c r="N19" s="16">
+      <c r="N19" s="32">
         <v>84.36</v>
       </c>
-      <c r="O19" s="17">
+      <c r="O19" s="33">
         <v>84.36</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="43">
-        <f>B6/B$12</f>
+      <c r="B20" s="38">
+        <f t="shared" si="5"/>
         <v>0.11315389014792163</v>
       </c>
-      <c r="C20" s="43">
-        <f>C6/C$12</f>
+      <c r="C20" s="38">
+        <f t="shared" si="5"/>
         <v>0.12461951181313198</v>
       </c>
-      <c r="D20" s="43">
-        <f>D6/D$12</f>
+      <c r="D20" s="38">
+        <f t="shared" si="5"/>
         <v>8.7282731974147626E-2</v>
       </c>
-      <c r="E20" s="43">
-        <f>E6/E$12</f>
+      <c r="E20" s="38">
+        <f t="shared" si="5"/>
         <v>0.17252526081911815</v>
       </c>
-      <c r="F20" s="44">
-        <f t="shared" ref="F20:F25" si="4">AVERAGE(B20:E20)</f>
+      <c r="F20" s="39">
+        <f t="shared" ref="F20:F25" si="6">AVERAGE(B20:E20)</f>
         <v>0.12439534868857985</v>
       </c>
-      <c r="G20" s="40"/>
+      <c r="G20" s="35"/>
       <c r="T20">
         <v>2021</v>
       </c>
@@ -1963,27 +1957,27 @@
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="43">
-        <f>B7/B$12</f>
+      <c r="B21" s="38">
+        <f t="shared" si="5"/>
         <v>0.46491021260418985</v>
       </c>
-      <c r="C21" s="43">
-        <f>C7/C$12</f>
+      <c r="C21" s="38">
+        <f t="shared" si="5"/>
         <v>0.45995180272461117</v>
       </c>
-      <c r="D21" s="43">
-        <f>D7/D$12</f>
+      <c r="D21" s="38">
+        <f t="shared" si="5"/>
         <v>0.47374441737167422</v>
       </c>
-      <c r="E21" s="43">
-        <f>E7/E$12</f>
+      <c r="E21" s="38">
+        <f t="shared" si="5"/>
         <v>0.47767654226134793</v>
       </c>
-      <c r="F21" s="44">
-        <f t="shared" si="4"/>
+      <c r="F21" s="39">
+        <f t="shared" si="6"/>
         <v>0.46907074374045576</v>
       </c>
       <c r="S21" t="s">
@@ -1994,141 +1988,287 @@
         <v>886.48299999999995</v>
       </c>
       <c r="U21" s="3">
-        <f t="shared" ref="U21:W21" si="5">SUM(U4:U18)</f>
+        <f t="shared" ref="U21:W21" si="7">SUM(U4:U18)</f>
         <v>791.74599999999987</v>
       </c>
       <c r="V21" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>921.38499999999999</v>
       </c>
       <c r="W21" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>912.89700000000005</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="43">
-        <f>B8/B$12</f>
+      <c r="B22" s="38">
+        <f t="shared" si="5"/>
         <v>8.0783275031782897E-2</v>
       </c>
-      <c r="C22" s="43">
-        <f>C8/C$12</f>
+      <c r="C22" s="38">
+        <f t="shared" si="5"/>
         <v>4.6003389976078182E-2</v>
       </c>
-      <c r="D22" s="43">
-        <f>D8/D$12</f>
+      <c r="D22" s="38">
+        <f t="shared" si="5"/>
         <v>2.9880017582226755E-2</v>
       </c>
-      <c r="E22" s="43">
-        <f>E8/E$12</f>
+      <c r="E22" s="38">
+        <f t="shared" si="5"/>
         <v>2.6181127184326511E-2</v>
       </c>
-      <c r="F22" s="44">
-        <f t="shared" si="4"/>
+      <c r="F22" s="39">
+        <f t="shared" si="6"/>
         <v>4.5711952443603585E-2</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="43">
-        <f>B9/B$12</f>
+      <c r="B23" s="38">
+        <f t="shared" si="5"/>
         <v>0.10066746908852173</v>
       </c>
-      <c r="C23" s="43">
-        <f>C9/C$12</f>
+      <c r="C23" s="38">
+        <f t="shared" si="5"/>
         <v>0.10071159184890102</v>
       </c>
-      <c r="D23" s="43">
-        <f>D9/D$12</f>
+      <c r="D23" s="38">
+        <f t="shared" si="5"/>
         <v>0.11952658226474276</v>
       </c>
-      <c r="E23" s="43">
-        <f>E9/E$12</f>
+      <c r="E23" s="38">
+        <f t="shared" si="5"/>
         <v>0.10765111771243575</v>
       </c>
-      <c r="F23" s="44">
-        <f t="shared" si="4"/>
+      <c r="F23" s="39">
+        <f t="shared" si="6"/>
         <v>0.10713919022865032</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="43">
-        <f>B10/B$12</f>
+      <c r="B24" s="38">
+        <f t="shared" si="5"/>
         <v>4.1647724773063902E-2</v>
       </c>
-      <c r="C24" s="43">
-        <f>C10/C$12</f>
+      <c r="C24" s="38">
+        <f t="shared" si="5"/>
         <v>6.7749000310705701E-2</v>
       </c>
-      <c r="D24" s="43">
-        <f>D10/D$12</f>
+      <c r="D24" s="38">
+        <f t="shared" si="5"/>
         <v>5.8216706371386553E-2</v>
       </c>
-      <c r="E24" s="43">
-        <f>E10/E$12</f>
+      <c r="E24" s="38">
+        <f t="shared" si="5"/>
         <v>5.2432633742804442E-2</v>
       </c>
-      <c r="F24" s="44">
-        <f t="shared" si="4"/>
+      <c r="F24" s="39">
+        <f t="shared" si="6"/>
         <v>5.5011516299490151E-2</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="45">
-        <f>B11/B$12</f>
+      <c r="B25" s="40">
+        <f t="shared" si="5"/>
         <v>6.5517330845599978E-2</v>
       </c>
-      <c r="C25" s="45">
-        <f>C11/C$12</f>
+      <c r="C25" s="40">
+        <f t="shared" si="5"/>
         <v>0.10654932263630001</v>
       </c>
-      <c r="D25" s="45">
-        <f>D11/D$12</f>
+      <c r="D25" s="40">
+        <f t="shared" si="5"/>
         <v>9.1557817850301454E-2</v>
       </c>
-      <c r="E25" s="45">
-        <f>E11/E$12</f>
+      <c r="E25" s="40">
+        <f t="shared" si="5"/>
         <v>8.2461166714074996E-2</v>
       </c>
-      <c r="F25" s="46">
-        <f t="shared" si="4"/>
+      <c r="F25" s="41">
+        <f t="shared" si="6"/>
         <v>8.6521409511569114E-2</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="45">
-        <f>B12/B$12</f>
+      <c r="B26" s="40">
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="C26" s="45">
-        <f>C12/C$12</f>
+      <c r="C26" s="40">
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="D26" s="45">
-        <f>D12/D$12</f>
+      <c r="D26" s="40">
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="E26" s="45">
-        <f>E12/E$12</f>
+      <c r="E26" s="40">
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="F26" s="47">
+      <c r="F26" s="42">
         <f>F12/F$12</f>
         <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A30" t="str">
+        <f t="array" ref="A30:I34">TRANSPOSE(A4:E12)</f>
+        <v>Fleet Group</v>
+      </c>
+      <c r="B30" t="str">
+        <v>G1</v>
+      </c>
+      <c r="C30" t="str">
+        <v>G2</v>
+      </c>
+      <c r="D30" t="str">
+        <v>G3</v>
+      </c>
+      <c r="E30" t="str">
+        <v>G4</v>
+      </c>
+      <c r="F30" t="str">
+        <v>G5</v>
+      </c>
+      <c r="G30" t="str">
+        <v>G6</v>
+      </c>
+      <c r="H30" t="str">
+        <v>G7</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Total</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A31">
+        <v>2021</v>
+      </c>
+      <c r="B31">
+        <v>118.18600000000001</v>
+      </c>
+      <c r="C31">
+        <v>100.309</v>
+      </c>
+      <c r="D31">
+        <v>412.13499999999999</v>
+      </c>
+      <c r="E31">
+        <v>71.613</v>
+      </c>
+      <c r="F31">
+        <v>89.24</v>
+      </c>
+      <c r="G31">
+        <v>36.92</v>
+      </c>
+      <c r="H31">
+        <v>58.08</v>
+      </c>
+      <c r="I31">
+        <v>886.48299999999995</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <v>2022</v>
+      </c>
+      <c r="B32">
+        <v>74.753</v>
+      </c>
+      <c r="C32">
+        <v>98.667000000000002</v>
+      </c>
+      <c r="D32">
+        <v>364.16500000000002</v>
+      </c>
+      <c r="E32">
+        <v>36.423000000000002</v>
+      </c>
+      <c r="F32">
+        <v>79.738</v>
+      </c>
+      <c r="G32">
+        <v>53.64</v>
+      </c>
+      <c r="H32">
+        <v>84.36</v>
+      </c>
+      <c r="I32">
+        <v>791.74600000000009</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <v>2023</v>
+      </c>
+      <c r="B33">
+        <v>128.80199999999999</v>
+      </c>
+      <c r="C33">
+        <v>80.421000000000006</v>
+      </c>
+      <c r="D33">
+        <v>436.50100000000003</v>
+      </c>
+      <c r="E33">
+        <v>27.530999999999999</v>
+      </c>
+      <c r="F33">
+        <v>110.13000000000001</v>
+      </c>
+      <c r="G33">
+        <v>53.64</v>
+      </c>
+      <c r="H33">
+        <v>84.36</v>
+      </c>
+      <c r="I33">
+        <v>921.38499999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <v>2024</v>
+      </c>
+      <c r="B34">
+        <v>82.938999999999993</v>
+      </c>
+      <c r="C34">
+        <v>176.49799999999999</v>
+      </c>
+      <c r="D34">
+        <v>488.67599999999999</v>
+      </c>
+      <c r="E34">
+        <v>26.783999999999999</v>
+      </c>
+      <c r="F34">
+        <v>110.13000000000001</v>
+      </c>
+      <c r="G34">
+        <v>53.64</v>
+      </c>
+      <c r="H34">
+        <v>84.36</v>
+      </c>
+      <c r="I34">
+        <v>1023.027</v>
       </c>
     </row>
   </sheetData>
